--- a/collection-template.xlsx
+++ b/collection-template.xlsx
@@ -741,7 +741,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -9861,7 +9861,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -13509,7 +13509,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
@@ -15865,7 +15865,7 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
@@ -16929,7 +16929,7 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
@@ -17043,7 +17043,7 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
@@ -17271,7 +17271,7 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
@@ -18107,7 +18107,7 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
@@ -18183,7 +18183,7 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
@@ -18411,7 +18411,7 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
@@ -19247,7 +19247,7 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
@@ -19475,7 +19475,7 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
@@ -19589,7 +19589,7 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
@@ -19627,7 +19627,7 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
@@ -20083,7 +20083,7 @@
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
@@ -21983,7 +21983,7 @@
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
@@ -22287,7 +22287,7 @@
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G575" t="inlineStr">
@@ -23237,7 +23237,7 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
@@ -23351,7 +23351,7 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
@@ -24263,7 +24263,7 @@
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
@@ -24453,7 +24453,7 @@
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G632" t="inlineStr">
@@ -24567,7 +24567,7 @@
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
@@ -25669,7 +25669,7 @@
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
@@ -26581,7 +26581,7 @@
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
@@ -26809,7 +26809,7 @@
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
@@ -26847,7 +26847,7 @@
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
@@ -27683,7 +27683,7 @@
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -27835,7 +27835,7 @@
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
@@ -28557,7 +28557,7 @@
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
@@ -28633,7 +28633,7 @@
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
@@ -28785,7 +28785,7 @@
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">

--- a/collection-template.xlsx
+++ b/collection-template.xlsx
@@ -9841,7 +9841,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Daughter of the Void</t>
+          <t>Kai'sa, Daughter of the Void</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9917,7 +9917,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Relentless Storm</t>
+          <t>Volibear, Relentless Storm</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Loose Cannon</t>
+          <t>Jinx, Loose Cannon</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Hand of Noxus</t>
+          <t>Darius, Hand of Noxus</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Nine-Tailed Fox</t>
+          <t>Ahri, Nine-Tailed Fox</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -10221,7 +10221,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Blind Monk</t>
+          <t>Lee Sin, Blind Monk</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -10297,7 +10297,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Unforgiven</t>
+          <t>Yasuo, Unforgiven</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Radiant Dawn</t>
+          <t>Leona, Radiant Dawn</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Swift Scout</t>
+          <t>Teemo, Swift Scout</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Herald of the Arcane</t>
+          <t>Viktor, Herald of the Arcane</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Bounty Hunter</t>
+          <t>Miss Fortune, Bounty Hunter</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>The Boss</t>
+          <t>Sett, The Boss</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -12463,7 +12463,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Dark Child - Starter</t>
+          <t>Annie, Dark Child</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Wuju Bladesman - Starter</t>
+          <t>Master Yi, Wuju Bladesman</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Lady of Luminosity - Starter</t>
+          <t>Lux, Lady of Luminosity</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Might of Demacia - Starter</t>
+          <t>Garen, Might of Demacia</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -19607,7 +19607,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Mechanized Menace</t>
+          <t>Rumble, Mechanized Menace</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -19683,7 +19683,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Purifier</t>
+          <t>Lucian, Purifier</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -19759,7 +19759,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Glorious Executioner</t>
+          <t>Draven, Glorious Executioner</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -19835,7 +19835,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Void Burrower</t>
+          <t>Reksai, Void Burrower</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -19911,7 +19911,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Fire Below the Mountain</t>
+          <t>Ornn, Fire Below the Mountain</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -20063,7 +20063,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Grandmaster at Arms</t>
+          <t>Jax, Grandmaster at Arms</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Blade Dancer</t>
+          <t>Irelia, Blade Dancer</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -20215,7 +20215,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Emperor of the Sands</t>
+          <t>Azir, Emperor of the Sands</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Prodigal Explorer</t>
+          <t>Ezreal, Prodigal Explorer</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Chem-Baroness</t>
+          <t>Renata Glasc, Chem-Baroness</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -20443,7 +20443,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Battle Mistress</t>
+          <t>Sivir, Battle Mistress</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -20519,7 +20519,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Grand Duelist</t>
+          <t>Fiora, Grand Duelist</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -28005,7 +28005,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>Virtuoso</t>
+          <t>Jhin, Virtuoso</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -28081,7 +28081,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Pridestalker</t>
+          <t>Rengar, Pridestalker</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -28157,7 +28157,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Bloodharbor Ripper</t>
+          <t>Pyke, Bloodharbor Ripper</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Piltover Enforcer</t>
+          <t>Vi, Piltover Enforcer</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -28309,7 +28309,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Bashful Bloom</t>
+          <t>Lillia, Bashful Bloom</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -28385,7 +28385,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Wuju Master</t>
+          <t>Master Yi, Wuju Master</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -28461,7 +28461,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Gloomist</t>
+          <t>Vex, Gloomist</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -28537,7 +28537,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Green Father</t>
+          <t>Ivern, Green Father</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -28613,7 +28613,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Scorn of the Moon</t>
+          <t>Diana, Scorn of the Moon</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -28689,7 +28689,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Deceiver</t>
+          <t>Leblanc, Deceiver</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -28765,7 +28765,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Voidreaver</t>
+          <t>Khazix, Voidreaver</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -28841,7 +28841,7 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Keeper of the Hammer</t>
+          <t>Poppy, Keeper of the Hammer</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">

--- a/collection-template.xlsx
+++ b/collection-template.xlsx
@@ -9937,7 +9937,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -10545,7 +10545,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
@@ -19323,7 +19323,7 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
@@ -28329,7 +28329,7 @@
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>showcase</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">

--- a/collection-template.xlsx
+++ b/collection-template.xlsx
@@ -19835,7 +19835,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Reksai, Void Burrower</t>
+          <t>Rek'Sai, Void Burrower</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">

--- a/collection-template.xlsx
+++ b/collection-template.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Collection" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Collection'!$A$1:$H$764</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Collection'!$A$1:$H$930</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H764"/>
+  <dimension ref="A1:H930"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -29479,8 +29479,6316 @@
       </c>
       <c r="H764" s="2" t="inlineStr"/>
     </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>details-baccai-sandspinner</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Baccai Sandspinner</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>fury</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H765" s="2" t="inlineStr"/>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>details-blade-twirler</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Blade Twirler</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>fury</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H766" s="2" t="inlineStr"/>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>details-brittle-steel</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Brittle Steel</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>fury</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H767" s="2" t="inlineStr"/>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>details-dune-surfer</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Dune Surfer</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>fury</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H768" s="2" t="inlineStr"/>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>details-forsaken-baccai</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Forsaken Baccai</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>fury</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H769" s="2" t="inlineStr"/>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>details-oasis-raider</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Oasis Raider</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>fury</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H770" s="2" t="inlineStr"/>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>details-punching-poro</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Punching Poro</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>fury</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H771" s="2" t="inlineStr"/>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>details-ruthless-strike</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>Ruthless Strike</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>fury</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H772" s="2" t="inlineStr"/>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>details-baccai-reaper</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>Baccai Reaper</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>fury</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H773" s="2" t="inlineStr"/>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>details-consuming-curse</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Consuming Curse</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>fury</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H774" s="2" t="inlineStr"/>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>details-pendulum-blade</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Pendulum Blade</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>fury</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>gear</t>
+        </is>
+      </c>
+      <c r="H775" s="2" t="inlineStr"/>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>details-perfect-execution</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Perfect Execution</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>fury</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H776" s="2" t="inlineStr"/>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>details-shadow-assassin</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>Shadow Assassin</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>fury</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H777" s="2" t="inlineStr"/>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>details-shadow-fiend</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>Shadow Fiend</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>fury</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H778" s="2" t="inlineStr"/>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>details-decree-of-rage</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>Decree of Rage</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>fury</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H779" s="2" t="inlineStr"/>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>details-eclipse-dragon</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>Eclipse Dragon</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>fury</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H780" s="2" t="inlineStr"/>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>details-morgana-vindictive</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>Morgana, Vindictive</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>fury</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H781" s="2" t="inlineStr"/>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>details-rage-amplifier</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>Rage Amplifier</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>fury</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>gear</t>
+        </is>
+      </c>
+      <c r="H782" s="2" t="inlineStr"/>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>details-renekton-rage-fueled</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Renekton, Rage Fueled</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>fury</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H783" s="2" t="inlineStr"/>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>details-twilight-reveler</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Twilight Reveler</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>fury</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H784" s="2" t="inlineStr"/>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>details-akali-deadly-weapon</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Akali, Deadly Weapon</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>fury</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H785" s="2" t="inlineStr"/>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>details-endless-riches</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>Endless Riches</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>fury</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>gear</t>
+        </is>
+      </c>
+      <c r="H786" s="2" t="inlineStr"/>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>details-zed-from-the-shadows</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>Zed, From the Shadows</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>fury</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H787" s="2" t="inlineStr"/>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>details-affectionate-poro</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>Affectionate Poro</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H788" s="2" t="inlineStr"/>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>details-esteemed-hierophant</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Esteemed Hierophant</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H789" s="2" t="inlineStr"/>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>details-field-musicians</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Field Musicians</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H790" s="2" t="inlineStr"/>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>details-hand-hammer</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Hand Hammer</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>gear</t>
+        </is>
+      </c>
+      <c r="H791" s="2" t="inlineStr"/>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>details-mournful-witness</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Mournful Witness</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H792" s="2" t="inlineStr"/>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>details-ol-poro</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>Ol' Poro</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H793" s="2" t="inlineStr"/>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>details-serene-ascetic</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>Serene Ascetic</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H794" s="2" t="inlineStr"/>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>details-twilight-shroud</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Twilight Shroud</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H795" s="2" t="inlineStr"/>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>details-frostcoat-mother</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Frostcoat Mother</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H796" s="2" t="inlineStr"/>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>details-pakaa-protector</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Pakaa Protector</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H797" s="2" t="inlineStr"/>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>details-resonating-strike</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Resonating Strike</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H798" s="2" t="inlineStr"/>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>details-sanction</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Sanction</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H799" s="2" t="inlineStr"/>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>details-sandstone-chimera</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Sandstone Chimera</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H800" s="2" t="inlineStr"/>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>details-tomb-raider-barbara</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>Tomb-Raider Barbara</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H801" s="2" t="inlineStr"/>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>details-akali-silent</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>Akali, Silent</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H802" s="2" t="inlineStr"/>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>details-crumbling-sands</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Crumbling Sands</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H803" s="2" t="inlineStr"/>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>details-decree-of-focus</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Decree of Focus</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H804" s="2" t="inlineStr"/>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>details-riven-shattered</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Riven, Shattered</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H805" s="2" t="inlineStr"/>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>details-shen-scourge-of-shadows</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Shen, Scourge of Shadows</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H806" s="2" t="inlineStr"/>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>details-steel-paws</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Steel Paws</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H807" s="2" t="inlineStr"/>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>details-astral-heron</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Astral Heron</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H808" s="2" t="inlineStr"/>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>details-helm-of-suppression</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Helm of Suppression</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>gear</t>
+        </is>
+      </c>
+      <c r="H809" s="2" t="inlineStr"/>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>details-nasus-ascended</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Nasus, Ascended</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H810" s="2" t="inlineStr"/>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>details-apprentice-mage</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Apprentice Mage</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>mind</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H811" s="2" t="inlineStr"/>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>details-cloud-drake</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Cloud Drake</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>mind</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H812" s="2" t="inlineStr"/>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>details-dredge-up</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Dredge Up</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>mind</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H813" s="2" t="inlineStr"/>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>details-grumpy-rockbear</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Grumpy Rockbear</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>mind</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H814" s="2" t="inlineStr"/>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>details-iterative-design</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Iterative Design</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>mind</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H815" s="2" t="inlineStr"/>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>details-mesmerize</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Mesmerize</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>mind</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H816" s="2" t="inlineStr"/>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>details-otterpus</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Otterpus</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>mind</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H817" s="2" t="inlineStr"/>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>details-questionable-tome</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Questionable Tome</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>mind</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>gear</t>
+        </is>
+      </c>
+      <c r="H818" s="2" t="inlineStr"/>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>details-applied-researchers</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Applied Researchers</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>mind</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H819" s="2" t="inlineStr"/>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>details-clairvoyance</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Clairvoyance</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>mind</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H820" s="2" t="inlineStr"/>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>details-covert-informant</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Covert Informant</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>mind</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H821" s="2" t="inlineStr"/>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>details-patched-porobot</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Patched Porobot</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>mind</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H822" s="2" t="inlineStr"/>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>details-shock-blast</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Shock Blast</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>mind</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H823" s="2" t="inlineStr"/>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>details-sky-cruiser</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Sky Cruiser</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>mind</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H824" s="2" t="inlineStr"/>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>details-decree-of-insight</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Decree of Insight</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>mind</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H825" s="2" t="inlineStr"/>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>details-hextech-formula</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Hextech Formula</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>mind</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>gear</t>
+        </is>
+      </c>
+      <c r="H826" s="2" t="inlineStr"/>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>details-nasus-guardian-of-knowledge</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Nasus, Guardian of Knowledge</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>mind</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H827" s="2" t="inlineStr"/>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>details-plaza-guardian</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Plaza Guardian</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>mind</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H828" s="2" t="inlineStr"/>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>details-swain-visionary</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Swain, Visionary</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>mind</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H829" s="2" t="inlineStr"/>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>details-temporal-breach</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Temporal Breach</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>mind</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H830" s="2" t="inlineStr"/>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>details-bottled-constellation</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Bottled Constellation</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>mind</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>gear</t>
+        </is>
+      </c>
+      <c r="H831" s="2" t="inlineStr"/>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>details-jayce-brilliant-inventor</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Jayce, Brilliant Inventor</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>mind</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H832" s="2" t="inlineStr"/>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>details-mel-newly-awakened</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Mel, Newly Awakened</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>mind</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H833" s="2" t="inlineStr"/>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>details-brutal-hunter</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Brutal Hunter</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H834" s="2" t="inlineStr"/>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>details-fretful-feline</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Fretful Feline</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H835" s="2" t="inlineStr"/>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>details-guttural-roar</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Guttural Roar</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H836" s="2" t="inlineStr"/>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>details-jagged-cutlass</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Jagged Cutlass</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>gear</t>
+        </is>
+      </c>
+      <c r="H837" s="2" t="inlineStr"/>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>details-legion-marauder</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>Legion Marauder</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H838" s="2" t="inlineStr"/>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>details-platewyrm-egg</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>Platewyrm Egg</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>gear</t>
+        </is>
+      </c>
+      <c r="H839" s="2" t="inlineStr"/>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>details-repair-specialist</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>Repair Specialist</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H840" s="2" t="inlineStr"/>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>details-tools-of-empire</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>Tools of Empire</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>gear</t>
+        </is>
+      </c>
+      <c r="H841" s="2" t="inlineStr"/>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>details-baccai-witherclaw</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Baccai Witherclaw</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H842" s="2" t="inlineStr"/>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>details-dame-the-despoiler</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>Dame the Despoiler</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H843" s="2" t="inlineStr"/>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>details-noxian-demolitionist</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>Noxian Demolitionist</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H844" s="2" t="inlineStr"/>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>details-onslaught</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Onslaught</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H845" s="2" t="inlineStr"/>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>details-profiteer</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Profiteer</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H846" s="2" t="inlineStr"/>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>details-rampage</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>Rampage</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H847" s="2" t="inlineStr"/>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>details-ambessa-the-wolf</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>Ambessa, The Wolf</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H848" s="2" t="inlineStr"/>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>details-decree-of-strength</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Decree of Strength</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H849" s="2" t="inlineStr"/>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>details-gangplank-naval</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>Gangplank, Naval</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H850" s="2" t="inlineStr"/>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>details-hextech-disc</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Hextech Disc</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>gear</t>
+        </is>
+      </c>
+      <c r="H851" s="2" t="inlineStr"/>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>details-jayce-hammer-in-hand</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Jayce, Hammer in Hand</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H852" s="2" t="inlineStr"/>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>details-wild-claw</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Wild Claw</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H853" s="2" t="inlineStr"/>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>details-cataclysmic-duel</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>Cataclysmic Duel</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H854" s="2" t="inlineStr"/>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>details-corrupted-dragon</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Corrupted Dragon</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H855" s="2" t="inlineStr"/>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>details-renekton-brute</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>Renekton, Brute</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H856" s="2" t="inlineStr"/>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>details-kinkou-lifeblade</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Kinkou Lifeblade</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H857" s="2" t="inlineStr"/>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>details-mask-mother</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Mask Mother</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H858" s="2" t="inlineStr"/>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>details-shadow-order-disciple</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Shadow Order Disciple</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H859" s="2" t="inlineStr"/>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>details-shadowblade-lurker</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Shadowblade Lurker</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H860" s="2" t="inlineStr"/>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>details-spiderling</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>Spiderling</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H861" s="2" t="inlineStr"/>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>details-stargazer</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>Stargazer</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H862" s="2" t="inlineStr"/>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>details-tornado-warrior</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Tornado Warrior</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H863" s="2" t="inlineStr"/>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>details-up-from-the-deep</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Up from the Deep</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H864" s="2" t="inlineStr"/>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>details-gust-monk</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Gust Monk</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H865" s="2" t="inlineStr"/>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>details-ravenbloom-prefect</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Ravenbloom Prefect</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H866" s="2" t="inlineStr"/>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>details-shadows-of-the-past</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>Shadows of the Past</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H867" s="2" t="inlineStr"/>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>details-tail-cloaked-matriarch</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>Tail-Cloaked Matriarch</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H868" s="2" t="inlineStr"/>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>details-twilight-step</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>Twilight Step</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H869" s="2" t="inlineStr"/>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>details-wind-and-ghosts</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Wind and Ghosts</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H870" s="2" t="inlineStr"/>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>details-decree-of-discord</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Decree of Discord</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H871" s="2" t="inlineStr"/>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>details-forgotten-relic</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Forgotten Relic</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>gear</t>
+        </is>
+      </c>
+      <c r="H872" s="2" t="inlineStr"/>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>details-illaoi-prophet-of-the-great-kraken</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Illaoi, Prophet of the Great Kraken</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H873" s="2" t="inlineStr"/>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>details-mel-defiant-soul</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>Mel, Defiant Soul</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H874" s="2" t="inlineStr"/>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>details-minah-swiftfoot</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Minah Swiftfoot</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H875" s="2" t="inlineStr"/>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>details-zed-without-a-sound</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Zed, Without a Sound</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H876" s="2" t="inlineStr"/>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>details-kennen-storm-of-shuriken</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>Kennen, Storm of Shuriken</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H877" s="2" t="inlineStr"/>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>details-kharox</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Kharox</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H878" s="2" t="inlineStr"/>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>details-ocean-drake</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>Ocean Drake</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H879" s="2" t="inlineStr"/>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>details-dragon-form</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Dragon Form</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H880" s="2" t="inlineStr"/>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>details-disciple-of-shen</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>Disciple of Shen</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H881" s="2" t="inlineStr"/>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>details-horns-of-the-dragon</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Horns of the Dragon</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H882" s="2" t="inlineStr"/>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>details-keeper-of-law</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Keeper of Law</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H883" s="2" t="inlineStr"/>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>details-masa-crashing-thunder</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Masa, Crashing Thunder</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H884" s="2" t="inlineStr"/>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>details-reluctant-leader</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Reluctant Leader</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H885" s="2" t="inlineStr"/>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>details-solari-sunhawk</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Solari Sunhawk</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H886" s="2" t="inlineStr"/>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>details-soulspinner</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Soulspinner</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H887" s="2" t="inlineStr"/>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>details-escaped-grayback</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Escaped Grayback</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H888" s="2" t="inlineStr"/>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>details-hungry-wolf</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Hungry Wolf</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H889" s="2" t="inlineStr"/>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>details-ki-barrier</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Ki Barrier</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H890" s="2" t="inlineStr"/>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>details-lacerate</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Lacerate</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H891" s="2" t="inlineStr"/>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>details-noxian-emissary</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Noxian Emissary</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H892" s="2" t="inlineStr"/>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>details-sacred-protector</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Sacred Protector</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H893" s="2" t="inlineStr"/>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>details-aurok-general</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Aurok General</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H894" s="2" t="inlineStr"/>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>details-decree-of-unity</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Decree of Unity</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H895" s="2" t="inlineStr"/>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>details-fallen-feline</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Fallen Feline</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H896" s="2" t="inlineStr"/>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>details-glowstone</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Glowstone</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>gear</t>
+        </is>
+      </c>
+      <c r="H897" s="2" t="inlineStr"/>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>details-kayle-justified</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Kayle, Justified</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H898" s="2" t="inlineStr"/>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>details-kennen-keeper-of-balance</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Kennen, Keeper of Balance</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H899" s="2" t="inlineStr"/>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>details-ambessa-respected-and-feared</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Ambessa, Respected and Feared</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H900" s="2" t="inlineStr"/>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>details-shady-spectacles</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Shady Spectacles</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>gear</t>
+        </is>
+      </c>
+      <c r="H901" s="2" t="inlineStr"/>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>details-shen-leader-of-the-kinkou-order</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Shen, Leader of the Kinkou Order</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="H902" s="2" t="inlineStr"/>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>details-akali-rogue-assassin</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Akali, Rogue Assassin</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>fury, calm</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>legend</t>
+        </is>
+      </c>
+      <c r="H903" s="2" t="inlineStr"/>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>details-shuriken-flip</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Shuriken Flip</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>fury, calm</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H904" s="2" t="inlineStr"/>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>details-renekton-butcher-of-the-sands</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Renekton, Butcher of the Sands</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>fury, body</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>legend</t>
+        </is>
+      </c>
+      <c r="H905" s="2" t="inlineStr"/>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>details-dominus</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Dominus</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>fury, body</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H906" s="2" t="inlineStr"/>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>details-zed-master-of-shadows</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Zed, Master of Shadows</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>fury, chaos</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>legend</t>
+        </is>
+      </c>
+      <c r="H907" s="2" t="inlineStr"/>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>details-death-mark</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Death Mark</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>fury, chaos</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H908" s="2" t="inlineStr"/>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>details-nasus-curator-of-the-sands</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Nasus, Curator of the Sands</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>calm, mind</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>legend</t>
+        </is>
+      </c>
+      <c r="H909" s="2" t="inlineStr"/>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>details-siphoning-strike</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Siphoning Strike</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>calm, mind</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H910" s="2" t="inlineStr"/>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>details-shen-eye-of-twilight</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Shen, Eye of Twilight</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>calm, order</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>legend</t>
+        </is>
+      </c>
+      <c r="H911" s="2" t="inlineStr"/>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>details-shadow-dash</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Shadow Dash</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>calm, order</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H912" s="2" t="inlineStr"/>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>details-jayce-defender-of-tomorrow</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>Jayce, Defender of Tomorrow</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>mind, body</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>legend</t>
+        </is>
+      </c>
+      <c r="H913" s="2" t="inlineStr"/>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>details-acceleration-gate</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Acceleration Gate</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>mind, body</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H914" s="2" t="inlineStr"/>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>details-mel-souls-reflection</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Mel, Soul's Reflection</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>mind, chaos</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>legend</t>
+        </is>
+      </c>
+      <c r="H915" s="2" t="inlineStr"/>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>details-rebuttal</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Rebuttal</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>mind, chaos</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H916" s="2" t="inlineStr"/>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>details-ambessa-matriarch-of-war</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Ambessa, Matriarch of War</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>body, order</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>legend</t>
+        </is>
+      </c>
+      <c r="H917" s="2" t="inlineStr"/>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>details-public-execution</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Public Execution</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>body, order</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H918" s="2" t="inlineStr"/>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>details-yordle-heart-of-the-tempest</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Yordle, Heart of the Tempest</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>order, chaos</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>legend</t>
+        </is>
+      </c>
+      <c r="H919" s="2" t="inlineStr"/>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>details-lightning-rush</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Lightning Rush</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>order, chaos</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="H920" s="2" t="inlineStr"/>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>details-dragon-roost</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Dragon Roost</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>colorless</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>battlefield</t>
+        </is>
+      </c>
+      <c r="H921" s="2" t="inlineStr"/>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>details-heisho-shell-of-the-world</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>Heisho, Shell of the World</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>colorless</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>battlefield</t>
+        </is>
+      </c>
+      <c r="H922" s="2" t="inlineStr"/>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>details-kinkou-temple</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Kinkou Temple</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>colorless</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>battlefield</t>
+        </is>
+      </c>
+      <c r="H923" s="2" t="inlineStr"/>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>details-mystic-vortex</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Mystic Vortex</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>colorless</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>battlefield</t>
+        </is>
+      </c>
+      <c r="H924" s="2" t="inlineStr"/>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>details-piltovan-forge</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Piltovan Forge</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>colorless</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>battlefield</t>
+        </is>
+      </c>
+      <c r="H925" s="2" t="inlineStr"/>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>details-protective-sands</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Protective Sands</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>colorless</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>battlefield</t>
+        </is>
+      </c>
+      <c r="H926" s="2" t="inlineStr"/>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>details-risen-altar</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Risen Altar</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>colorless</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>battlefield</t>
+        </is>
+      </c>
+      <c r="H927" s="2" t="inlineStr"/>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>details-sandswept-tomb</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Sandswept Tomb</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>colorless</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>battlefield</t>
+        </is>
+      </c>
+      <c r="H928" s="2" t="inlineStr"/>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>details-shadow-temple</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Shadow Temple</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>colorless</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>battlefield</t>
+        </is>
+      </c>
+      <c r="H929" s="2" t="inlineStr"/>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>details-threshold-of-the-gray</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>Threshold of the Gray</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>colorless</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>battlefield</t>
+        </is>
+      </c>
+      <c r="H930" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H764"/>
+  <autoFilter ref="A1:H930"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>